--- a/paper-data/2026-10-19/journal.xlsx
+++ b/paper-data/2026-10-19/journal.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1552,6 +1552,252 @@
         <v>533.7253490608521</v>
       </c>
       <c r="V14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:27:59</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SELL_SHORT</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>168.7756</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.0666</v>
+      </c>
+      <c r="H15" t="n">
+        <v>348.79</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout short through prior low 168.86 flags=['inside_day'] EXPERIMENTAL | ctx: context filter not used by this rule (matches backtest)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>171.4934</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>163.3399</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
+        <v>168.8600006103516</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:55:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>254.172</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.1781</v>
+      </c>
+      <c r="H16" t="n">
+        <v>299.44</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout short through prior low 254.00 flags=['NR7', 'inside_day'] EXPERIMENTAL</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.118</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>EOD_FLATTEN_1455</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>08:44:58</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>253.873</v>
+      </c>
+      <c r="P16" t="n">
+        <v>255.4834</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>250.6523</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="S16" t="n">
+        <v>370</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
+        <v>254.0449981689453</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:55:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LIVE-PAPER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY_COVER</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>167.8039</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.0666</v>
+      </c>
+      <c r="H17" t="n">
+        <v>346.78</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NR7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NR7/inside breakout short through prior low 168.86 flags=['inside_day'] EXPERIMENTAL</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>EOD_FLATTEN_1455</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>13:27:59</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>168.7756</v>
+      </c>
+      <c r="P17" t="n">
+        <v>171.4934</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>163.3399</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>87</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="U17" t="n">
+        <v>167.7200012207031</v>
+      </c>
+      <c r="V17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1566,7 +1812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1624,49 +1870,6 @@
         <is>
           <t>unrealized_usd</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NR7</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>08:44:58</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>253.873</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.1781</v>
-      </c>
-      <c r="G2" t="n">
-        <v>299.09</v>
-      </c>
-      <c r="H2" t="n">
-        <v>255.4834</v>
-      </c>
-      <c r="I2" t="n">
-        <v>250.6523</v>
-      </c>
-      <c r="J2" t="n">
-        <v>253.0700073242188</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -1994,13 +2197,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.66</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -2060,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2122,6 +2331,106 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>997.6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>697.84</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>997</v>
+      </c>
+      <c r="C4" t="n">
+        <v>697.84</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>996.33</v>
+      </c>
+      <c r="C5" t="n">
+        <v>349.05</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>995.08</v>
+      </c>
+      <c r="C6" t="n">
+        <v>349.05</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2171,7 +2480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 11:30:25</t>
+          <t>2026-10-19 15:01:00</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>997.87</v>
+        <v>998.58</v>
       </c>
     </row>
     <row r="6">
@@ -2202,7 +2511,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>697.84</v>
+        <v>998.58</v>
       </c>
     </row>
     <row r="7">
@@ -2212,7 +2521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2222,7 +2531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2232,7 +2541,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.129</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="10">
@@ -2242,7 +2551,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2252,7 +2561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2272,7 +2581,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.17</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -2282,7 +2591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
